--- a/data/attendance/ECOLE_فوج_سمية.xlsx
+++ b/data/attendance/ECOLE_فوج_سمية.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
@@ -23,13 +20,6 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:f8905006-9bee-471d-8f12-eb0cd71fbdc5</t>
         </r>
       </text>
@@ -37,13 +27,6 @@
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d133b1c1-28a3-4b97-a9db-6b476ae244b4</t>
         </r>
       </text>
@@ -51,13 +34,6 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:17558c2a-1262-434a-97e3-56eca8a756b1</t>
         </r>
       </text>
@@ -65,13 +41,6 @@
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:706ecf15-8a21-4df2-9994-901d88ca9cdc</t>
         </r>
       </text>
@@ -79,13 +48,6 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:abbf565a-6277-46a7-9673-f053d01d6e24</t>
         </r>
       </text>
@@ -93,210 +55,175 @@
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+          <t>student_id:c2c5e8ca-a7bd-45e8-9793-c7720b5f46fc</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0">
+      <text>
+        <r>
           <t>student_id:59b4f620-8e75-44c0-aadf-45cabeb9141e</t>
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
           <t>student_id:c01f45e3-eec2-4c07-b9aa-1b000085c506</t>
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
           <t>student_id:44b5cb5d-f5f3-40f1-a42d-2a355c517e79</t>
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
           <t>student_id:ac87ac71-9fcb-4f92-bef9-33417995d6ec</t>
         </r>
       </text>
     </comment>
-    <comment ref="B14" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <t>student_id:d4541bbb-072f-4861-a46c-930b232417f4</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0">
+      <text>
+        <r>
           <t>student_id:d22b3e6b-1630-40f5-91b3-7b6fc7e4ad05</t>
         </r>
       </text>
     </comment>
-    <comment ref="B15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B17" authorId="0">
+      <text>
+        <r>
+          <t>student_id:9a762dcc-0f03-41b4-9dfa-98fd9988b2d0</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
           <t>student_id:94e004eb-8b38-4922-81eb-3f96b2c303d6</t>
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B19" authorId="0">
+      <text>
+        <r>
           <t>student_id:77645cae-b930-4c71-806f-3ddb4cb7ea8f</t>
         </r>
       </text>
     </comment>
-    <comment ref="B17" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B20" authorId="0">
+      <text>
+        <r>
           <t>student_id:c8af8d9b-3c42-46eb-9c42-203634cf2e3c</t>
         </r>
       </text>
     </comment>
-    <comment ref="B18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B21" authorId="0">
+      <text>
+        <r>
           <t>student_id:2c46242e-72a9-4689-9f55-78b5a8eea43a</t>
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B22" authorId="0">
+      <text>
+        <r>
           <t>student_id:a21d3c38-fda8-49e6-b528-2330f3f14726</t>
         </r>
       </text>
     </comment>
-    <comment ref="B20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B23" authorId="0">
+      <text>
+        <r>
           <t>student_id:86d1ef6c-eb6f-476d-9d7e-46259ece3a03</t>
         </r>
       </text>
     </comment>
-    <comment ref="B21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B24" authorId="0">
+      <text>
+        <r>
           <t>student_id:8160c99d-64b1-4b4d-8150-143c0e624600</t>
         </r>
       </text>
     </comment>
-    <comment ref="B22" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B25" authorId="0">
+      <text>
+        <r>
           <t>student_id:c1165679-eeca-44a1-b1a1-e448620e5a98</t>
         </r>
       </text>
     </comment>
-    <comment ref="B23" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B26" authorId="0">
+      <text>
+        <r>
           <t>student_id:bb0837e1-6cfe-4c9e-b897-9dbf23a118f6</t>
         </r>
       </text>
     </comment>
-    <comment ref="B24" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+    <comment ref="B27" authorId="0">
+      <text>
+        <r>
           <t>student_id:5350077d-06e9-4bbb-8108-020e37dc82e2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0">
+      <text>
+        <r>
+          <t>student_id:12a42856-482e-4a71-9cd5-99790f02e3b2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0">
+      <text>
+        <r>
+          <t>student_id:8102bdd5-6665-4405-9175-8781f2718f0b</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0">
+      <text>
+        <r>
+          <t>student_id:11db9800-a1a7-4572-a486-51cc7786393f</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0">
+      <text>
+        <r>
+          <t>student_id:13bac5d2-33bf-465a-b2dd-549cd1d97521</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0">
+      <text>
+        <r>
+          <t>student_id:0dfd348e-db58-464a-8d1c-b58f9cf1d2ca</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0">
+      <text>
+        <r>
+          <t>student_id:cd266631-af81-4f02-9c3c-84de83af4377</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0">
+      <text>
+        <r>
+          <t>student_id:5f48dd6f-9904-496b-8c4a-2b615499043d</t>
         </r>
       </text>
     </comment>
@@ -305,7 +232,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
   <si>
     <t>فوج سمية  |  ECOLE  |  BAC  |  عطية الله سمية</t>
   </si>
@@ -319,6 +246,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -340,6 +270,12 @@
     <t>24/09/2026</t>
   </si>
   <si>
+    <t>01/10/2026</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -358,6 +294,9 @@
     <t>حطاب ميسون</t>
   </si>
   <si>
+    <t>حمودي مريم</t>
+  </si>
+  <si>
     <t>ناصر سيرين</t>
   </si>
   <si>
@@ -370,9 +309,15 @@
     <t>سعدوني يحيى</t>
   </si>
   <si>
+    <t>بن عثمان رتاج</t>
+  </si>
+  <si>
     <t>قاسمي رنيم</t>
   </si>
   <si>
+    <t>بطاش سفيان</t>
+  </si>
+  <si>
     <t>بن مرخي دعاء</t>
   </si>
   <si>
@@ -403,6 +348,27 @@
     <t>حوحامدي مروة</t>
   </si>
   <si>
+    <t>محمودي  ماجدة</t>
+  </si>
+  <si>
+    <t>بن المير جنة دعاء</t>
+  </si>
+  <si>
+    <t>قطيش اسماء</t>
+  </si>
+  <si>
+    <t>فراح تقوى</t>
+  </si>
+  <si>
+    <t>خوجة سيرين</t>
+  </si>
+  <si>
+    <t>حميمد تسنيم</t>
+  </si>
+  <si>
+    <t>حيمود جواد</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -430,7 +396,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -452,40 +421,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="666666"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -572,7 +534,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -927,15 +889,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N34"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -953,7 +915,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -963,10 +925,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -985,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
@@ -1008,66 +973,66 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>6</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="8">
         <v>0</v>
@@ -1094,24 +1059,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>220</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9">
         <v>0</v>
@@ -1138,24 +1103,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>232</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="8">
         <v>0</v>
@@ -1182,24 +1147,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>233</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="9">
         <v>0</v>
@@ -1226,24 +1191,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>241</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
       </c>
       <c r="D9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="8">
         <v>0</v>
@@ -1270,663 +1235,1103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
+        <v>248</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>253</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="9">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9">
-        <v>1</v>
-      </c>
-      <c r="F10" s="9">
-        <v>1</v>
-      </c>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-      <c r="N10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="B11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>294</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8">
-        <v>1</v>
-      </c>
-      <c r="G11" s="8">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8">
-        <v>0</v>
-      </c>
-      <c r="N11" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="B12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>299</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="9">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9">
-        <v>1</v>
-      </c>
-      <c r="F12" s="9">
-        <v>1</v>
-      </c>
-      <c r="G12" s="9">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>0</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="9">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9">
-        <v>0</v>
-      </c>
-      <c r="N12" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="B13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>307</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8">
-        <v>1</v>
-      </c>
-      <c r="G13" s="8">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8">
-        <v>0</v>
-      </c>
-      <c r="K13" s="8">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="8">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="B14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>308</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
         <v>321</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="9">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9">
-        <v>1</v>
-      </c>
-      <c r="E14" s="9">
-        <v>1</v>
-      </c>
-      <c r="F14" s="9">
-        <v>1</v>
-      </c>
-      <c r="G14" s="9">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="B16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>324</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>393</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="8">
-        <v>1</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8">
-        <v>1</v>
-      </c>
-      <c r="G15" s="8">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8">
-        <v>0</v>
-      </c>
-      <c r="M15" s="8">
-        <v>0</v>
-      </c>
-      <c r="N15" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="B18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
         <v>578</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="9">
-        <v>1</v>
-      </c>
-      <c r="D16" s="9">
-        <v>1</v>
-      </c>
-      <c r="E16" s="9">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9">
-        <v>1</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9">
-        <v>0</v>
-      </c>
-      <c r="L16" s="9">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-      <c r="N16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="B19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
         <v>579</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8">
-        <v>1</v>
-      </c>
-      <c r="G17" s="8">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8">
-        <v>0</v>
-      </c>
-      <c r="J17" s="8">
-        <v>0</v>
-      </c>
-      <c r="K17" s="8">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8">
-        <v>0</v>
-      </c>
-      <c r="N17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="B20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
         <v>580</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="9">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9">
-        <v>0</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9">
-        <v>1</v>
-      </c>
-      <c r="G18" s="9">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>0</v>
-      </c>
-      <c r="I18" s="9">
-        <v>0</v>
-      </c>
-      <c r="J18" s="9">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9">
-        <v>0</v>
-      </c>
-      <c r="L18" s="9">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="B21" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
         <v>581</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="8">
-        <v>1</v>
-      </c>
-      <c r="D19" s="8">
-        <v>1</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1</v>
-      </c>
-      <c r="F19" s="8">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8">
-        <v>0</v>
-      </c>
-      <c r="I19" s="8">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8">
-        <v>0</v>
-      </c>
-      <c r="K19" s="8">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8">
-        <v>0</v>
-      </c>
-      <c r="M19" s="8">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="B22" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
         <v>582</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="9">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9">
-        <v>0</v>
-      </c>
-      <c r="E20" s="9">
-        <v>1</v>
-      </c>
-      <c r="F20" s="9">
-        <v>1</v>
-      </c>
-      <c r="G20" s="9">
-        <v>0</v>
-      </c>
-      <c r="H20" s="9">
-        <v>0</v>
-      </c>
-      <c r="I20" s="9">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9">
-        <v>0</v>
-      </c>
-      <c r="L20" s="9">
-        <v>0</v>
-      </c>
-      <c r="M20" s="9">
-        <v>0</v>
-      </c>
-      <c r="N20" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="B23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8">
+        <v>0</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
+      <c r="N23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
         <v>583</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="8">
-        <v>1</v>
-      </c>
-      <c r="D21" s="8">
-        <v>1</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0</v>
-      </c>
-      <c r="F21" s="8">
-        <v>1</v>
-      </c>
-      <c r="G21" s="8">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8">
-        <v>0</v>
-      </c>
-      <c r="J21" s="8">
-        <v>0</v>
-      </c>
-      <c r="K21" s="8">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8">
-        <v>0</v>
-      </c>
-      <c r="N21" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="B24" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9">
+        <v>0</v>
+      </c>
+      <c r="M24" s="9">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
         <v>584</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="9">
-        <v>0</v>
-      </c>
-      <c r="D22" s="9">
-        <v>0</v>
-      </c>
-      <c r="E22" s="9">
-        <v>1</v>
-      </c>
-      <c r="F22" s="9">
-        <v>1</v>
-      </c>
-      <c r="G22" s="9">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9">
-        <v>0</v>
-      </c>
-      <c r="I22" s="9">
-        <v>0</v>
-      </c>
-      <c r="J22" s="9">
-        <v>0</v>
-      </c>
-      <c r="K22" s="9">
-        <v>0</v>
-      </c>
-      <c r="L22" s="9">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9">
-        <v>0</v>
-      </c>
-      <c r="N22" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="B25" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="8">
+        <v>0</v>
+      </c>
+      <c r="D25" s="8">
+        <v>0</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
         <v>585</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="8">
-        <v>0</v>
-      </c>
-      <c r="D23" s="8">
-        <v>0</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0</v>
-      </c>
-      <c r="F23" s="8">
-        <v>1</v>
-      </c>
-      <c r="G23" s="8">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8">
-        <v>0</v>
-      </c>
-      <c r="I23" s="8">
-        <v>0</v>
-      </c>
-      <c r="J23" s="8">
-        <v>0</v>
-      </c>
-      <c r="K23" s="8">
-        <v>0</v>
-      </c>
-      <c r="L23" s="8">
-        <v>0</v>
-      </c>
-      <c r="M23" s="8">
-        <v>0</v>
-      </c>
-      <c r="N23" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="B26" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0</v>
+      </c>
+      <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9">
+        <v>0</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
         <v>586</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="9">
-        <v>0</v>
-      </c>
-      <c r="D24" s="9">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0</v>
-      </c>
-      <c r="F24" s="9">
-        <v>1</v>
-      </c>
-      <c r="G24" s="9">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9">
-        <v>0</v>
-      </c>
-      <c r="I24" s="9">
-        <v>0</v>
-      </c>
-      <c r="J24" s="9">
-        <v>0</v>
-      </c>
-      <c r="K24" s="9">
-        <v>0</v>
-      </c>
-      <c r="L24" s="9">
-        <v>0</v>
-      </c>
-      <c r="M24" s="9">
-        <v>0</v>
-      </c>
-      <c r="N24" s="9">
+      <c r="B27" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0</v>
+      </c>
+      <c r="D27" s="8">
+        <v>0</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8">
+        <v>0</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+      <c r="N27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>651</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>0</v>
+      </c>
+      <c r="I28" s="9">
+        <v>0</v>
+      </c>
+      <c r="J28" s="9">
+        <v>0</v>
+      </c>
+      <c r="K28" s="9">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9">
+        <v>0</v>
+      </c>
+      <c r="M28" s="9">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>827</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8">
+        <v>0</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
+      <c r="N29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>946</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
+      <c r="J30" s="9">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9">
+        <v>0</v>
+      </c>
+      <c r="L30" s="9">
+        <v>0</v>
+      </c>
+      <c r="M30" s="9">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>947</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0</v>
+      </c>
+      <c r="D31" s="8">
+        <v>0</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8">
+        <v>0</v>
+      </c>
+      <c r="M31" s="8">
+        <v>0</v>
+      </c>
+      <c r="N31" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>954</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>0</v>
+      </c>
+      <c r="I32" s="9">
+        <v>0</v>
+      </c>
+      <c r="J32" s="9">
+        <v>0</v>
+      </c>
+      <c r="K32" s="9">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9">
+        <v>0</v>
+      </c>
+      <c r="M32" s="9">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>955</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0</v>
+      </c>
+      <c r="D33" s="8">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8">
+        <v>0</v>
+      </c>
+      <c r="M33" s="8">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>956</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>0</v>
+      </c>
+      <c r="I34" s="9">
+        <v>0</v>
+      </c>
+      <c r="J34" s="9">
+        <v>0</v>
+      </c>
+      <c r="K34" s="9">
+        <v>0</v>
+      </c>
+      <c r="L34" s="9">
+        <v>0</v>
+      </c>
+      <c r="M34" s="9">
+        <v>0</v>
+      </c>
+      <c r="N34" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1936,7 +2341,7 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1946,89 +2351,94 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>